--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784619</v>
+        <v>136785929</v>
       </c>
       <c r="B9" t="n">
-        <v>78863</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414034</v>
+        <v>414089</v>
       </c>
       <c r="R9" t="n">
-        <v>6966236</v>
+        <v>6966357</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784625</v>
+        <v>135784619</v>
       </c>
       <c r="B10" t="n">
-        <v>79217</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414064</v>
+        <v>414034</v>
       </c>
       <c r="R10" t="n">
-        <v>6966335</v>
+        <v>6966236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784621</v>
+        <v>135784625</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414048</v>
+        <v>414064</v>
       </c>
       <c r="R11" t="n">
-        <v>6966257</v>
+        <v>6966335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784618</v>
+        <v>135784621</v>
       </c>
       <c r="B12" t="n">
-        <v>78464</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414032</v>
+        <v>414048</v>
       </c>
       <c r="R12" t="n">
-        <v>6966235</v>
+        <v>6966257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
+          <t>https://artportalen.se/Sighting/135784621</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784617</v>
+        <v>135784618</v>
       </c>
       <c r="B13" t="n">
-        <v>80050</v>
+        <v>78464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414033</v>
+        <v>414032</v>
       </c>
       <c r="R13" t="n">
-        <v>6966234</v>
+        <v>6966235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,38 +1902,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
+          <t>https://artportalen.se/Sighting/135784618</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784620</v>
+        <v>135784617</v>
       </c>
       <c r="B14" t="n">
-        <v>92349</v>
+        <v>80050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6008693</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414048</v>
+        <v>414033</v>
       </c>
       <c r="R14" t="n">
-        <v>6966257</v>
+        <v>6966234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,18 +1981,12 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,6 +2003,216 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784617</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136785995</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>414095</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6966334</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136785995</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135784620</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92349</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -2029,6 +2233,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784630</v>
+        <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>92267</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414080</v>
+        <v>414093</v>
       </c>
       <c r="R4" t="n">
-        <v>6966366</v>
+        <v>6966365</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/136827967</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784624</v>
+        <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414061</v>
+        <v>414106</v>
       </c>
       <c r="R5" t="n">
-        <v>6966238</v>
+        <v>6966426</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136827971</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784627</v>
+        <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414083</v>
+        <v>414101</v>
       </c>
       <c r="R6" t="n">
-        <v>6966332</v>
+        <v>6966420</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/136827972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784623</v>
+        <v>135784630</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>92267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414075</v>
+        <v>414080</v>
       </c>
       <c r="R7" t="n">
-        <v>6966258</v>
+        <v>6966366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784628</v>
+        <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>92292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414097</v>
+        <v>414090</v>
       </c>
       <c r="R8" t="n">
-        <v>6966344</v>
+        <v>6966346</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/136827969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136785929</v>
+        <v>135784624</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>92141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414089</v>
+        <v>414061</v>
       </c>
       <c r="R9" t="n">
-        <v>6966357</v>
+        <v>6966238</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784619</v>
+        <v>135784627</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>92141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414034</v>
+        <v>414083</v>
       </c>
       <c r="R10" t="n">
-        <v>6966236</v>
+        <v>6966332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784625</v>
+        <v>135784623</v>
       </c>
       <c r="B11" t="n">
-        <v>79217</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414064</v>
+        <v>414075</v>
       </c>
       <c r="R11" t="n">
-        <v>6966335</v>
+        <v>6966258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784621</v>
+        <v>135784628</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414048</v>
+        <v>414097</v>
       </c>
       <c r="R12" t="n">
-        <v>6966257</v>
+        <v>6966344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784618</v>
+        <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>78464</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414032</v>
+        <v>414089</v>
       </c>
       <c r="R13" t="n">
-        <v>6966235</v>
+        <v>6966357</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784617</v>
+        <v>135784619</v>
       </c>
       <c r="B14" t="n">
-        <v>80050</v>
+        <v>78863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414033</v>
+        <v>414034</v>
       </c>
       <c r="R14" t="n">
-        <v>6966234</v>
+        <v>6966236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136785995</v>
+        <v>135784625</v>
       </c>
       <c r="B15" t="n">
-        <v>80066</v>
+        <v>79217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414095</v>
+        <v>414064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966334</v>
+        <v>6966335</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784620</v>
+        <v>135784621</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>80079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6008693</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,18 +2185,12 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2213,6 +2207,828 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784621</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784618</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>414032</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966235</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136827966</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>414060</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966372</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827966</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136827968</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>414092</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827968</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136827973</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>414054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966456</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827973</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135784617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>414033</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6966234</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784617</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136785995</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>414095</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6966334</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136785995</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136827970</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>414107</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6966416</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827970</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135784620</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -2235,6 +3051,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827967</v>
+        <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414093</v>
+        <v>414080</v>
       </c>
       <c r="R4" t="n">
-        <v>6966365</v>
+        <v>6966366</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827967</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136827971</v>
+        <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414106</v>
+        <v>414061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966426</v>
+        <v>6966238</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827971</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136827972</v>
+        <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414101</v>
+        <v>414083</v>
       </c>
       <c r="R6" t="n">
-        <v>6966420</v>
+        <v>6966332</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827972</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784630</v>
+        <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>92267</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414080</v>
+        <v>414075</v>
       </c>
       <c r="R7" t="n">
-        <v>6966366</v>
+        <v>6966258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136827969</v>
+        <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>92292</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414090</v>
+        <v>414097</v>
       </c>
       <c r="R8" t="n">
-        <v>6966346</v>
+        <v>6966344</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827969</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784624</v>
+        <v>136785929</v>
       </c>
       <c r="B9" t="n">
-        <v>92141</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414061</v>
+        <v>414089</v>
       </c>
       <c r="R9" t="n">
-        <v>6966238</v>
+        <v>6966357</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784627</v>
+        <v>135784619</v>
       </c>
       <c r="B10" t="n">
-        <v>92141</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414083</v>
+        <v>414034</v>
       </c>
       <c r="R10" t="n">
-        <v>6966332</v>
+        <v>6966236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784623</v>
+        <v>135784625</v>
       </c>
       <c r="B11" t="n">
-        <v>93386</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414075</v>
+        <v>414064</v>
       </c>
       <c r="R11" t="n">
-        <v>6966258</v>
+        <v>6966335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784628</v>
+        <v>135784621</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414097</v>
+        <v>414048</v>
       </c>
       <c r="R12" t="n">
-        <v>6966344</v>
+        <v>6966257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/135784621</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136785929</v>
+        <v>135784618</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>78464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414089</v>
+        <v>414032</v>
       </c>
       <c r="R13" t="n">
-        <v>6966357</v>
+        <v>6966235</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784618</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784619</v>
+        <v>135784617</v>
       </c>
       <c r="B14" t="n">
-        <v>78863</v>
+        <v>80050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414034</v>
+        <v>414033</v>
       </c>
       <c r="R14" t="n">
-        <v>6966236</v>
+        <v>6966234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784617</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135784625</v>
+        <v>136785995</v>
       </c>
       <c r="B15" t="n">
-        <v>79217</v>
+        <v>80066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414064</v>
+        <v>414095</v>
       </c>
       <c r="R15" t="n">
-        <v>6966335</v>
+        <v>6966334</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/136785995</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784621</v>
+        <v>135784620</v>
       </c>
       <c r="B16" t="n">
-        <v>80079</v>
+        <v>92349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6008693</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Antrodia crassa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,12 +2185,18 @@
           <t>2026-08-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2207,828 +2213,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135784618</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78464</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>414032</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6966235</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136827966</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79234</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>414060</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6966372</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827966</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136827968</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79234</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>414092</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6966352</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827968</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>136827973</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79234</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>414054</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6966456</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827973</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135784617</v>
-      </c>
-      <c r="B21" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>414033</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6966234</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>136785995</v>
-      </c>
-      <c r="B22" t="n">
-        <v>80066</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>414095</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6966334</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>136827970</v>
-      </c>
-      <c r="B23" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>414107</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6966416</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827970</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135784620</v>
-      </c>
-      <c r="B24" t="n">
-        <v>92349</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6008693</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Kritporing</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Antrodia crassa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>414048</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6966257</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -3051,14 +2235,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784630</v>
+        <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>92267</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414080</v>
+        <v>414093</v>
       </c>
       <c r="R4" t="n">
-        <v>6966366</v>
+        <v>6966365</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/136827967</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784624</v>
+        <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414061</v>
+        <v>414106</v>
       </c>
       <c r="R5" t="n">
-        <v>6966238</v>
+        <v>6966426</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136827971</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784627</v>
+        <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414083</v>
+        <v>414101</v>
       </c>
       <c r="R6" t="n">
-        <v>6966332</v>
+        <v>6966420</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/136827972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784623</v>
+        <v>135784630</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>92267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414075</v>
+        <v>414080</v>
       </c>
       <c r="R7" t="n">
-        <v>6966258</v>
+        <v>6966366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784628</v>
+        <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>92292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414097</v>
+        <v>414090</v>
       </c>
       <c r="R8" t="n">
-        <v>6966344</v>
+        <v>6966346</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/136827969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136785929</v>
+        <v>135784624</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>92141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414089</v>
+        <v>414061</v>
       </c>
       <c r="R9" t="n">
-        <v>6966357</v>
+        <v>6966238</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784619</v>
+        <v>135784627</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>92141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414034</v>
+        <v>414083</v>
       </c>
       <c r="R10" t="n">
-        <v>6966236</v>
+        <v>6966332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784625</v>
+        <v>135784623</v>
       </c>
       <c r="B11" t="n">
-        <v>79217</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414064</v>
+        <v>414075</v>
       </c>
       <c r="R11" t="n">
-        <v>6966335</v>
+        <v>6966258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784621</v>
+        <v>135784628</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414048</v>
+        <v>414097</v>
       </c>
       <c r="R12" t="n">
-        <v>6966257</v>
+        <v>6966344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784618</v>
+        <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>78464</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414032</v>
+        <v>414089</v>
       </c>
       <c r="R13" t="n">
-        <v>6966235</v>
+        <v>6966357</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784617</v>
+        <v>135784619</v>
       </c>
       <c r="B14" t="n">
-        <v>80050</v>
+        <v>78863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414033</v>
+        <v>414034</v>
       </c>
       <c r="R14" t="n">
-        <v>6966234</v>
+        <v>6966236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136785995</v>
+        <v>135784625</v>
       </c>
       <c r="B15" t="n">
-        <v>80066</v>
+        <v>79217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414095</v>
+        <v>414064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966334</v>
+        <v>6966335</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784620</v>
+        <v>135784621</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>80079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6008693</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,18 +2185,12 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2213,6 +2207,828 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784621</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784618</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>414032</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966235</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136827966</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>414060</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966372</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827966</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136827968</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>414092</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827968</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136827973</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>414054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966456</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827973</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135784617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>414033</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6966234</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784617</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136785995</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>414095</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6966334</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136785995</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136827970</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>414107</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6966416</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827970</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135784620</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -2235,6 +3051,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827967</v>
+        <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414093</v>
+        <v>414080</v>
       </c>
       <c r="R4" t="n">
-        <v>6966365</v>
+        <v>6966366</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827967</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136827971</v>
+        <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414106</v>
+        <v>414061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966426</v>
+        <v>6966238</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827971</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136827972</v>
+        <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414101</v>
+        <v>414083</v>
       </c>
       <c r="R6" t="n">
-        <v>6966420</v>
+        <v>6966332</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827972</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784630</v>
+        <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>92267</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414080</v>
+        <v>414075</v>
       </c>
       <c r="R7" t="n">
-        <v>6966366</v>
+        <v>6966258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136827969</v>
+        <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>92303</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414090</v>
+        <v>414097</v>
       </c>
       <c r="R8" t="n">
-        <v>6966346</v>
+        <v>6966344</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827969</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784624</v>
+        <v>136785929</v>
       </c>
       <c r="B9" t="n">
-        <v>92141</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414061</v>
+        <v>414089</v>
       </c>
       <c r="R9" t="n">
-        <v>6966238</v>
+        <v>6966357</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784627</v>
+        <v>135784619</v>
       </c>
       <c r="B10" t="n">
-        <v>92141</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414083</v>
+        <v>414034</v>
       </c>
       <c r="R10" t="n">
-        <v>6966332</v>
+        <v>6966236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784623</v>
+        <v>135784625</v>
       </c>
       <c r="B11" t="n">
-        <v>93386</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414075</v>
+        <v>414064</v>
       </c>
       <c r="R11" t="n">
-        <v>6966258</v>
+        <v>6966335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784628</v>
+        <v>135784621</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414097</v>
+        <v>414048</v>
       </c>
       <c r="R12" t="n">
-        <v>6966344</v>
+        <v>6966257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/135784621</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136785929</v>
+        <v>135784618</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>78464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414089</v>
+        <v>414032</v>
       </c>
       <c r="R13" t="n">
-        <v>6966357</v>
+        <v>6966235</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784618</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784619</v>
+        <v>135784617</v>
       </c>
       <c r="B14" t="n">
-        <v>78863</v>
+        <v>80050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414034</v>
+        <v>414033</v>
       </c>
       <c r="R14" t="n">
-        <v>6966236</v>
+        <v>6966234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784617</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135784625</v>
+        <v>136785995</v>
       </c>
       <c r="B15" t="n">
-        <v>79217</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414064</v>
+        <v>414095</v>
       </c>
       <c r="R15" t="n">
-        <v>6966335</v>
+        <v>6966334</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/136785995</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784621</v>
+        <v>135784620</v>
       </c>
       <c r="B16" t="n">
-        <v>80079</v>
+        <v>92349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6008693</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Antrodia crassa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,12 +2185,18 @@
           <t>2026-08-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2207,828 +2213,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135784618</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78464</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>414032</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6966235</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136827966</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79241</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>414060</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6966372</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827966</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136827968</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79241</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>414092</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6966352</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827968</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>136827973</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79241</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>414054</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6966456</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827973</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135784617</v>
-      </c>
-      <c r="B21" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>414033</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6966234</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>136785995</v>
-      </c>
-      <c r="B22" t="n">
-        <v>80073</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>414095</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6966334</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>136827970</v>
-      </c>
-      <c r="B23" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>414107</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6966416</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827970</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135784620</v>
-      </c>
-      <c r="B24" t="n">
-        <v>92349</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6008693</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Kritporing</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Antrodia crassa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>414048</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6966257</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -3051,14 +2235,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784630</v>
+        <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>92267</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414080</v>
+        <v>414093</v>
       </c>
       <c r="R4" t="n">
-        <v>6966366</v>
+        <v>6966365</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/136827967</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784624</v>
+        <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414061</v>
+        <v>414106</v>
       </c>
       <c r="R5" t="n">
-        <v>6966238</v>
+        <v>6966426</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136827971</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784627</v>
+        <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414083</v>
+        <v>414101</v>
       </c>
       <c r="R6" t="n">
-        <v>6966332</v>
+        <v>6966420</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/136827972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784623</v>
+        <v>135784630</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>92267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414075</v>
+        <v>414080</v>
       </c>
       <c r="R7" t="n">
-        <v>6966258</v>
+        <v>6966366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784628</v>
+        <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>92307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414097</v>
+        <v>414090</v>
       </c>
       <c r="R8" t="n">
-        <v>6966344</v>
+        <v>6966346</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/136827969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136785929</v>
+        <v>135784624</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>92141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414089</v>
+        <v>414061</v>
       </c>
       <c r="R9" t="n">
-        <v>6966357</v>
+        <v>6966238</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784619</v>
+        <v>135784627</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>92141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414034</v>
+        <v>414083</v>
       </c>
       <c r="R10" t="n">
-        <v>6966236</v>
+        <v>6966332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784625</v>
+        <v>135784623</v>
       </c>
       <c r="B11" t="n">
-        <v>79217</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414064</v>
+        <v>414075</v>
       </c>
       <c r="R11" t="n">
-        <v>6966335</v>
+        <v>6966258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784621</v>
+        <v>135784628</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414048</v>
+        <v>414097</v>
       </c>
       <c r="R12" t="n">
-        <v>6966257</v>
+        <v>6966344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784618</v>
+        <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>78464</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414032</v>
+        <v>414089</v>
       </c>
       <c r="R13" t="n">
-        <v>6966235</v>
+        <v>6966357</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784617</v>
+        <v>135784619</v>
       </c>
       <c r="B14" t="n">
-        <v>80050</v>
+        <v>78863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414033</v>
+        <v>414034</v>
       </c>
       <c r="R14" t="n">
-        <v>6966234</v>
+        <v>6966236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136785995</v>
+        <v>135784625</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>79217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414095</v>
+        <v>414064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966334</v>
+        <v>6966335</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784620</v>
+        <v>135784621</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>80079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6008693</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,18 +2185,12 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2213,6 +2207,828 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784621</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784618</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>414032</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966235</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136827966</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>414060</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966372</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827966</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136827968</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>414092</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827968</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136827973</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>414054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966456</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827973</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135784617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>414033</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6966234</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784617</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136785995</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>414095</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6966334</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136785995</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136827970</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>414107</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6966416</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827970</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135784620</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -2235,6 +3051,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827967</v>
+        <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414093</v>
+        <v>414080</v>
       </c>
       <c r="R4" t="n">
-        <v>6966365</v>
+        <v>6966366</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827967</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136827971</v>
+        <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414106</v>
+        <v>414061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966426</v>
+        <v>6966238</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827971</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136827972</v>
+        <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414101</v>
+        <v>414083</v>
       </c>
       <c r="R6" t="n">
-        <v>6966420</v>
+        <v>6966332</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827972</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784630</v>
+        <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>92267</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414080</v>
+        <v>414075</v>
       </c>
       <c r="R7" t="n">
-        <v>6966366</v>
+        <v>6966258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136827969</v>
+        <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>92307</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414090</v>
+        <v>414097</v>
       </c>
       <c r="R8" t="n">
-        <v>6966346</v>
+        <v>6966344</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827969</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784624</v>
+        <v>136785929</v>
       </c>
       <c r="B9" t="n">
-        <v>92141</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414061</v>
+        <v>414089</v>
       </c>
       <c r="R9" t="n">
-        <v>6966238</v>
+        <v>6966357</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784627</v>
+        <v>135784619</v>
       </c>
       <c r="B10" t="n">
-        <v>92141</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414083</v>
+        <v>414034</v>
       </c>
       <c r="R10" t="n">
-        <v>6966332</v>
+        <v>6966236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784623</v>
+        <v>135784625</v>
       </c>
       <c r="B11" t="n">
-        <v>93386</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414075</v>
+        <v>414064</v>
       </c>
       <c r="R11" t="n">
-        <v>6966258</v>
+        <v>6966335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784628</v>
+        <v>135784621</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414097</v>
+        <v>414048</v>
       </c>
       <c r="R12" t="n">
-        <v>6966344</v>
+        <v>6966257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/135784621</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136785929</v>
+        <v>135784618</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>78464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414089</v>
+        <v>414032</v>
       </c>
       <c r="R13" t="n">
-        <v>6966357</v>
+        <v>6966235</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784618</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784619</v>
+        <v>135784617</v>
       </c>
       <c r="B14" t="n">
-        <v>78863</v>
+        <v>80050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414034</v>
+        <v>414033</v>
       </c>
       <c r="R14" t="n">
-        <v>6966236</v>
+        <v>6966234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784617</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135784625</v>
+        <v>136785995</v>
       </c>
       <c r="B15" t="n">
-        <v>79217</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414064</v>
+        <v>414095</v>
       </c>
       <c r="R15" t="n">
-        <v>6966335</v>
+        <v>6966334</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/136785995</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784621</v>
+        <v>135784620</v>
       </c>
       <c r="B16" t="n">
-        <v>80079</v>
+        <v>92349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6008693</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Antrodia crassa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,12 +2185,18 @@
           <t>2026-08-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2207,828 +2213,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135784618</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78464</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>414032</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6966235</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136827966</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>414060</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6966372</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827966</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136827968</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>414092</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6966352</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827968</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>136827973</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>414054</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6966456</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827973</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135784617</v>
-      </c>
-      <c r="B21" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>414033</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6966234</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>136785995</v>
-      </c>
-      <c r="B22" t="n">
-        <v>80075</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>414095</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6966334</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>136827970</v>
-      </c>
-      <c r="B23" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>414107</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6966416</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827970</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135784620</v>
-      </c>
-      <c r="B24" t="n">
-        <v>92349</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6008693</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Kritporing</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Antrodia crassa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>414048</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6966257</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -3051,14 +2235,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,48 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784630</v>
+        <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>92267</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414080</v>
+        <v>414093</v>
       </c>
       <c r="R4" t="n">
-        <v>6966366</v>
+        <v>6966365</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784630</t>
+          <t>https://artportalen.se/Sighting/136827967</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784624</v>
+        <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414061</v>
+        <v>414106</v>
       </c>
       <c r="R5" t="n">
-        <v>6966238</v>
+        <v>6966426</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1075,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784624</t>
+          <t>https://artportalen.se/Sighting/136827971</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784627</v>
+        <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414083</v>
+        <v>414101</v>
       </c>
       <c r="R6" t="n">
-        <v>6966332</v>
+        <v>6966420</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,49 +1177,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784627</t>
+          <t>https://artportalen.se/Sighting/136827972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784623</v>
+        <v>135784630</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>92267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414075</v>
+        <v>414080</v>
       </c>
       <c r="R7" t="n">
-        <v>6966258</v>
+        <v>6966366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784623</t>
+          <t>https://artportalen.se/Sighting/135784630</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784628</v>
+        <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>92309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414097</v>
+        <v>414090</v>
       </c>
       <c r="R8" t="n">
-        <v>6966344</v>
+        <v>6966346</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784628</t>
+          <t>https://artportalen.se/Sighting/136827969</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136785929</v>
+        <v>135784624</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>92141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414089</v>
+        <v>414061</v>
       </c>
       <c r="R9" t="n">
-        <v>6966357</v>
+        <v>6966238</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1483,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785929</t>
+          <t>https://artportalen.se/Sighting/135784624</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784619</v>
+        <v>135784627</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>92141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414034</v>
+        <v>414083</v>
       </c>
       <c r="R10" t="n">
-        <v>6966236</v>
+        <v>6966332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1596,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784619</t>
+          <t>https://artportalen.se/Sighting/135784627</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784625</v>
+        <v>135784623</v>
       </c>
       <c r="B11" t="n">
-        <v>79217</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414064</v>
+        <v>414075</v>
       </c>
       <c r="R11" t="n">
-        <v>6966335</v>
+        <v>6966258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,16 +1698,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784625</t>
+          <t>https://artportalen.se/Sighting/135784623</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784621</v>
+        <v>135784628</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414048</v>
+        <v>414097</v>
       </c>
       <c r="R12" t="n">
-        <v>6966257</v>
+        <v>6966344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,16 +1800,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784621</t>
+          <t>https://artportalen.se/Sighting/135784628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784618</v>
+        <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>78464</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414032</v>
+        <v>414089</v>
       </c>
       <c r="R13" t="n">
-        <v>6966235</v>
+        <v>6966357</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,27 +1891,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784618</t>
+          <t>https://artportalen.se/Sighting/136785929</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135784617</v>
+        <v>135784619</v>
       </c>
       <c r="B14" t="n">
-        <v>80050</v>
+        <v>78863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414033</v>
+        <v>414034</v>
       </c>
       <c r="R14" t="n">
-        <v>6966234</v>
+        <v>6966236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784617</t>
+          <t>https://artportalen.se/Sighting/135784619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136785995</v>
+        <v>135784625</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>79217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414095</v>
+        <v>414064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966334</v>
+        <v>6966335</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,49 +2095,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136785995</t>
+          <t>https://artportalen.se/Sighting/135784625</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784620</v>
+        <v>135784621</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>80079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6008693</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,18 +2185,12 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>För gammal fruktkropp för säker artbestämning.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2213,6 +2207,828 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784621</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784618</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>414032</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966235</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136827966</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>414060</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966372</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827966</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136827968</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>414092</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827968</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136827973</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>414054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966456</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827973</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135784617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>414033</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6966234</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784617</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136785995</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80078</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>414095</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6966334</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136785995</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136827970</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>414107</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6966416</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827970</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135784620</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784620</t>
         </is>
@@ -2235,6 +3051,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136785929</v>
       </c>
       <c r="B13" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136785995</v>
       </c>
       <c r="B22" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136827967</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136827971</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136827972</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136827969</v>
       </c>
       <c r="B8" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136827966</v>
       </c>
       <c r="B18" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136827968</v>
       </c>
       <c r="B19" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136827973</v>
       </c>
       <c r="B20" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136827970</v>
       </c>
       <c r="B23" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
